--- a/data/Lego_Liste_bereinigt.xlsx
+++ b/data/Lego_Liste_bereinigt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\Projects\Lego_Page\Brick_archiv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EB05B3-3BDA-4650-AEBC-4E8075ED9D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2126B6D-7AA6-4AEA-9A61-59F2A0C8877B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="534">
   <si>
     <t>Identifier</t>
   </si>
@@ -1622,6 +1622,9 @@
   </si>
   <si>
     <t>Ship in a Bottle</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -1992,12 +1995,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M252"/>
+  <dimension ref="A1:M280"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" customWidth="1"/>
     <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -9983,6 +9986,404 @@
         <v>22</v>
       </c>
     </row>
+    <row r="253" spans="1:13" ht="15.75">
+      <c r="B253" s="3">
+        <v>910065</v>
+      </c>
+      <c r="F253" s="4">
+        <v>1</v>
+      </c>
+      <c r="G253" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J253" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" ht="15.75">
+      <c r="B254" s="3">
+        <v>910066</v>
+      </c>
+      <c r="F254" s="4">
+        <v>1</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J254" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" ht="15.75">
+      <c r="B255" s="3">
+        <v>910066</v>
+      </c>
+      <c r="F255" s="4">
+        <v>1</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J255" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" ht="15.75">
+      <c r="B256" s="3">
+        <v>910064</v>
+      </c>
+      <c r="F256" s="4">
+        <v>1</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J256" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="257" spans="2:10" ht="15.75">
+      <c r="B257" s="3">
+        <v>910068</v>
+      </c>
+      <c r="F257" s="4">
+        <v>1</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J257" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="258" spans="2:10" ht="15.75">
+      <c r="B258" s="3">
+        <v>910067</v>
+      </c>
+      <c r="F258" s="4">
+        <v>1</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J258" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="259" spans="2:10" ht="15.75">
+      <c r="B259" s="3">
+        <v>30728</v>
+      </c>
+      <c r="F259" s="4">
+        <v>1</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J259" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="260" spans="2:10" ht="15.75">
+      <c r="B260" s="3">
+        <v>75435</v>
+      </c>
+      <c r="F260" s="4">
+        <v>1</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J260" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="261" spans="2:10" ht="15.75">
+      <c r="B261" s="3">
+        <v>40917</v>
+      </c>
+      <c r="F261" s="4">
+        <v>1</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J261" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="262" spans="2:10" ht="15.75">
+      <c r="B262" s="3">
+        <v>75442</v>
+      </c>
+      <c r="F262" s="4">
+        <v>1</v>
+      </c>
+      <c r="G262" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J262" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="263" spans="2:10" ht="15.75">
+      <c r="B263" s="3">
+        <v>5010320</v>
+      </c>
+      <c r="F263" s="4">
+        <v>1</v>
+      </c>
+      <c r="G263" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J263" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="264" spans="2:10" ht="15.75">
+      <c r="B264" s="3">
+        <v>40917</v>
+      </c>
+      <c r="F264" s="4">
+        <v>1</v>
+      </c>
+      <c r="G264" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J264" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="265" spans="2:10" ht="15.75">
+      <c r="B265" s="3">
+        <v>75442</v>
+      </c>
+      <c r="F265" s="4">
+        <v>1</v>
+      </c>
+      <c r="G265" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J265" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="266" spans="2:10" ht="15.75">
+      <c r="B266" s="3">
+        <v>75429</v>
+      </c>
+      <c r="F266" s="4">
+        <v>1</v>
+      </c>
+      <c r="G266" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J266" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="267" spans="2:10" ht="15.75">
+      <c r="B267" s="3">
+        <v>30727</v>
+      </c>
+      <c r="F267" s="4">
+        <v>1</v>
+      </c>
+      <c r="G267" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J267" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="268" spans="2:10" ht="15.75">
+      <c r="B268" s="3">
+        <v>75415</v>
+      </c>
+      <c r="F268" s="4">
+        <v>1</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J268" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="269" spans="2:10" ht="15.75">
+      <c r="B269" s="3">
+        <v>43010</v>
+      </c>
+      <c r="F269" s="4">
+        <v>1</v>
+      </c>
+      <c r="G269" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J269" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="270" spans="2:10" ht="15.75">
+      <c r="B270" s="3">
+        <v>40907</v>
+      </c>
+      <c r="F270" s="4">
+        <v>1</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J270" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="271" spans="2:10" ht="15.75">
+      <c r="B271" s="3">
+        <v>43021</v>
+      </c>
+      <c r="F271" s="4">
+        <v>1</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J271" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="272" spans="2:10" ht="15.75">
+      <c r="B272" s="3">
+        <v>40911</v>
+      </c>
+      <c r="F272" s="4">
+        <v>1</v>
+      </c>
+      <c r="G272" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J272" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="273" spans="2:10" ht="15.75">
+      <c r="B273" s="3">
+        <v>910059</v>
+      </c>
+      <c r="F273" s="4">
+        <v>1</v>
+      </c>
+      <c r="G273" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J273" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="274" spans="2:10" ht="15.75">
+      <c r="B274" s="3">
+        <v>910059</v>
+      </c>
+      <c r="F274" s="4">
+        <v>1</v>
+      </c>
+      <c r="G274" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J274" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="275" spans="2:10" ht="15.75">
+      <c r="B275" s="3">
+        <v>910060</v>
+      </c>
+      <c r="F275" s="4">
+        <v>1</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J275" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="276" spans="2:10" ht="15.75">
+      <c r="B276" s="3">
+        <v>910060</v>
+      </c>
+      <c r="F276" s="4">
+        <v>1</v>
+      </c>
+      <c r="G276" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J276" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="277" spans="2:10" ht="15.75">
+      <c r="B277" s="3">
+        <v>910062</v>
+      </c>
+      <c r="F277" s="4">
+        <v>1</v>
+      </c>
+      <c r="G277" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J277" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="278" spans="2:10" ht="15.75">
+      <c r="B278" s="3">
+        <v>910061</v>
+      </c>
+      <c r="F278" s="4">
+        <v>1</v>
+      </c>
+      <c r="G278" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J278" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="279" spans="2:10" ht="15.75">
+      <c r="B279" s="3">
+        <v>910063</v>
+      </c>
+      <c r="F279" s="4">
+        <v>1</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J279" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="280" spans="2:10" ht="15.75">
+      <c r="B280" s="3">
+        <v>910063</v>
+      </c>
+      <c r="F280" s="4">
+        <v>1</v>
+      </c>
+      <c r="G280" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H280" t="s">
+        <v>533</v>
+      </c>
+      <c r="I280" t="s">
+        <v>16</v>
+      </c>
+      <c r="J280" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M241" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
